--- a/artfynd/A 11770-2024 artfynd.xlsx
+++ b/artfynd/A 11770-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118791898</v>
+        <v>117943530</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,26 +710,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>hackmora, Dlr</t>
+          <t>Hackmora, Nedre, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513555</v>
+        <v>513550</v>
       </c>
       <c r="R2" t="n">
-        <v>6732290</v>
+        <v>6732264</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>detta är den sista och korrekta</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +784,11 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog som gränsar till myr. Blandbarrskog med stort lövinslag/mycket död ved, olika sphagnummossor. Mycket mygg!!!!</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117943530</v>
+        <v>118791898</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -836,30 +840,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hackmora, Nedre, Dlr</t>
+          <t>hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513550</v>
+        <v>513555</v>
       </c>
       <c r="R3" t="n">
-        <v>6732264</v>
+        <v>6732290</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,7 +898,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>detta är den sista och korrekta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,11 +915,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog som gränsar till myr. Blandbarrskog med stort lövinslag/mycket död ved, olika sphagnummossor. Mycket mygg!!!!</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 11770-2024 artfynd.xlsx
+++ b/artfynd/A 11770-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117943530</v>
+        <v>118791898</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,30 +710,26 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hackmora, Nedre, Dlr</t>
+          <t>hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513550</v>
+        <v>513555</v>
       </c>
       <c r="R2" t="n">
-        <v>6732264</v>
+        <v>6732290</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>detta är den sista och korrekta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,11 +785,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog som gränsar till myr. Blandbarrskog med stort lövinslag/mycket död ved, olika sphagnummossor. Mycket mygg!!!!</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -805,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118791898</v>
+        <v>117943091</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>100114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,49 +813,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>hackmora, Dlr</t>
+          <t>Hackmora nedre (Hackmora nedre), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513555</v>
+        <v>513478</v>
       </c>
       <c r="R3" t="n">
-        <v>6732290</v>
+        <v>6732117</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>detta är den sista och korrekta</t>
+          <t>Ett stort område med frisk, örtrik mark med blåsippsplantor. Det var otroligt med mygg, pga. myren och värmen, och jag kunde inte räkna plantorna men jag uppskattar att det minst finns flera hundra blåsippsplantor utspridda. 300 är en uppskattning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117943091</v>
+        <v>117943530</v>
       </c>
       <c r="B4" t="n">
-        <v>100107</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,30 +943,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -979,17 +979,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hackmora nedre (Hackmora nedre), Dlr</t>
+          <t>Hackmora, Nedre, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513478</v>
+        <v>513550</v>
       </c>
       <c r="R4" t="n">
-        <v>6732117</v>
+        <v>6732264</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,12 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett stort område med frisk, örtrik mark med blåsippsplantor. Det var otroligt med mygg, pga. myren och värmen, och jag kunde inte räkna plantorna men jag uppskattar att det minst finns flera hundra blåsippsplantor utspridda. 300 är en uppskattning.</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,6 +1040,11 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog som gränsar till myr. Blandbarrskog med stort lövinslag/mycket död ved, olika sphagnummossor. Mycket mygg!!!!</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 11770-2024 artfynd.xlsx
+++ b/artfynd/A 11770-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118791898</v>
+        <v>117943530</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -710,26 +710,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>hackmora, Dlr</t>
+          <t>Hackmora, Nedre, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513555</v>
+        <v>513550</v>
       </c>
       <c r="R2" t="n">
-        <v>6732290</v>
+        <v>6732264</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>detta är den sista och korrekta</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +784,11 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog som gränsar till myr. Blandbarrskog med stort lövinslag/mycket död ved, olika sphagnummossor. Mycket mygg!!!!</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117943091</v>
+        <v>118791898</v>
       </c>
       <c r="B3" t="n">
-        <v>100114</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,53 +817,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hackmora nedre (Hackmora nedre), Dlr</t>
+          <t>hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513478</v>
+        <v>513555</v>
       </c>
       <c r="R3" t="n">
-        <v>6732117</v>
+        <v>6732290</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett stort område med frisk, örtrik mark med blåsippsplantor. Det var otroligt med mygg, pga. myren och värmen, och jag kunde inte räkna plantorna men jag uppskattar att det minst finns flera hundra blåsippsplantor utspridda. 300 är en uppskattning.</t>
+          <t>detta är den sista och korrekta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117943530</v>
+        <v>117943091</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>100114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,30 +943,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -979,17 +979,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hackmora, Nedre, Dlr</t>
+          <t>Hackmora nedre (Hackmora nedre), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513550</v>
+        <v>513478</v>
       </c>
       <c r="R4" t="n">
-        <v>6732264</v>
+        <v>6732117</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett stort område med frisk, örtrik mark med blåsippsplantor. Det var otroligt med mygg, pga. myren och värmen, och jag kunde inte räkna plantorna men jag uppskattar att det minst finns flera hundra blåsippsplantor utspridda. 300 är en uppskattning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,11 +1045,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog som gränsar till myr. Blandbarrskog med stort lövinslag/mycket död ved, olika sphagnummossor. Mycket mygg!!!!</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
